--- a/artfynd/A 61718-2022 artfynd.xlsx
+++ b/artfynd/A 61718-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61718-2022 artfynd.xlsx
+++ b/artfynd/A 61718-2022 artfynd.xlsx
@@ -4427,7 +4427,7 @@
         <v>107953046</v>
       </c>
       <c r="B31" t="n">
-        <v>89412</v>
+        <v>90582</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692196.0545202596</v>
+        <v>692196</v>
       </c>
       <c r="R31" t="n">
-        <v>6603382.849667672</v>
+        <v>6603382</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4544,7 +4544,7 @@
         <v>107950268</v>
       </c>
       <c r="B32" t="n">
-        <v>8367</v>
+        <v>8421</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691942.1301243256</v>
+        <v>691942</v>
       </c>
       <c r="R32" t="n">
-        <v>6603370.37205842</v>
+        <v>6603371</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4666,7 +4666,7 @@
         <v>108478240</v>
       </c>
       <c r="B33" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692066.5236341339</v>
+        <v>692067</v>
       </c>
       <c r="R33" t="n">
-        <v>6603416.882525731</v>
+        <v>6603417</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4783,7 +4783,7 @@
         <v>109346216</v>
       </c>
       <c r="B34" t="n">
-        <v>93044</v>
+        <v>94311</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>692014.8860874517</v>
+        <v>692015</v>
       </c>
       <c r="R34" t="n">
-        <v>6603311.576628731</v>
+        <v>6603312</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4900,7 +4900,7 @@
         <v>108323070</v>
       </c>
       <c r="B35" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692066.468771309</v>
+        <v>692067</v>
       </c>
       <c r="R35" t="n">
-        <v>6603348.266898987</v>
+        <v>6603348</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -5017,7 +5017,7 @@
         <v>109346026</v>
       </c>
       <c r="B36" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692028.5766858526</v>
+        <v>692029</v>
       </c>
       <c r="R36" t="n">
-        <v>6603282.797859765</v>
+        <v>6603283</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -5143,7 +5143,7 @@
         <v>109345595</v>
       </c>
       <c r="B37" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692039.1380827061</v>
+        <v>692039</v>
       </c>
       <c r="R37" t="n">
-        <v>6603235.561497213</v>
+        <v>6603236</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5269,7 +5269,7 @@
         <v>108324470</v>
       </c>
       <c r="B38" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692004.8945581554</v>
+        <v>692005</v>
       </c>
       <c r="R38" t="n">
-        <v>6603397.467630562</v>
+        <v>6603397</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5386,7 +5386,7 @@
         <v>108322100</v>
       </c>
       <c r="B39" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692131.0267995562</v>
+        <v>692131</v>
       </c>
       <c r="R39" t="n">
-        <v>6603240.769164512</v>
+        <v>6603241</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5512,7 +5512,7 @@
         <v>109345310</v>
       </c>
       <c r="B40" t="n">
-        <v>89403</v>
+        <v>90573</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691961.9966769988</v>
+        <v>691962</v>
       </c>
       <c r="R40" t="n">
-        <v>6603210.779261133</v>
+        <v>6603211</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5629,7 +5629,7 @@
         <v>107950468</v>
       </c>
       <c r="B41" t="n">
-        <v>8367</v>
+        <v>8421</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691996.9554972184</v>
+        <v>691997</v>
       </c>
       <c r="R41" t="n">
-        <v>6603463.13239482</v>
+        <v>6603463</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5746,7 +5746,7 @@
         <v>109345480</v>
       </c>
       <c r="B42" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>692070.2018065801</v>
+        <v>692070</v>
       </c>
       <c r="R42" t="n">
-        <v>6603275.269424403</v>
+        <v>6603275</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5872,7 +5872,7 @@
         <v>109346315</v>
       </c>
       <c r="B43" t="n">
-        <v>77595</v>
+        <v>78615</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692015.0415873285</v>
+        <v>692015</v>
       </c>
       <c r="R43" t="n">
-        <v>6603308.535066666</v>
+        <v>6603308</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5989,7 +5989,7 @@
         <v>108478228</v>
       </c>
       <c r="B44" t="n">
-        <v>93375</v>
+        <v>94681</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>692049.6628273097</v>
+        <v>692050</v>
       </c>
       <c r="R44" t="n">
-        <v>6603418.053243431</v>
+        <v>6603418</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>

--- a/artfynd/A 61718-2022 artfynd.xlsx
+++ b/artfynd/A 61718-2022 artfynd.xlsx
@@ -4427,7 +4427,7 @@
         <v>107953046</v>
       </c>
       <c r="B31" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>108478240</v>
       </c>
       <c r="B33" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>109346216</v>
       </c>
       <c r="B34" t="n">
-        <v>94311</v>
+        <v>94334</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>108323070</v>
       </c>
       <c r="B35" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>109346026</v>
       </c>
       <c r="B36" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>109345595</v>
       </c>
       <c r="B37" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>108324470</v>
       </c>
       <c r="B38" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>108322100</v>
       </c>
       <c r="B39" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>109345310</v>
       </c>
       <c r="B40" t="n">
-        <v>90573</v>
+        <v>90591</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>109345480</v>
       </c>
       <c r="B42" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>109346315</v>
       </c>
       <c r="B43" t="n">
-        <v>78615</v>
+        <v>78631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>108478228</v>
       </c>
       <c r="B44" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 61718-2022 artfynd.xlsx
+++ b/artfynd/A 61718-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7151,6 +7151,123 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123526197</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56691</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storskogen, Storskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>691983</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6603386</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61718-2022 artfynd.xlsx
+++ b/artfynd/A 61718-2022 artfynd.xlsx
@@ -7156,7 +7156,7 @@
         <v>123526197</v>
       </c>
       <c r="B54" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>

--- a/artfynd/A 61718-2022 artfynd.xlsx
+++ b/artfynd/A 61718-2022 artfynd.xlsx
@@ -7156,7 +7156,7 @@
         <v>123526197</v>
       </c>
       <c r="B54" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
